--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lovecap\Documents\GitHub\NierGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D262D3A1-46E2-439F-B709-6724D70CB37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7813B467-8A8E-4091-A402-3631BAB20A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="作業工数見積もり" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$C$2:$G$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">作業工数見積もり!$C$2:$G$104</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="150">
   <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
@@ -516,55 +516,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>レーザー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ミラージュ(連続切り)</t>
-    <rPh sb="6" eb="8">
-      <t>レンゾク</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ブレード(プレイヤーの周囲を回る刀)</t>
-    <rPh sb="11" eb="13">
-      <t>シュウイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>カタナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>技セレクト(十字キーの右と左で切り替え)</t>
-    <rPh sb="0" eb="1">
-      <t>ワザ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジュウジ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ミギ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ヒダリ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ジャンプ(2回)</t>
     <rPh sb="6" eb="7">
       <t>カイ</t>
@@ -1240,6 +1191,9 @@
       <t>ダイニケイタイフク</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業中</t>
   </si>
 </sst>
 </file>
@@ -2131,8 +2085,8 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <f>SUM(作業工数見積もり!F5:F138)</f>
-        <v>81</v>
+        <f>SUM(作業工数見積もり!F5:F134)</f>
+        <v>79.25</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -2140,8 +2094,8 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <f>SUMIF(作業工数見積もり!G5:G63,"完了",作業工数見積もり!F5:F63)</f>
-        <v>38</v>
+        <f>SUMIF(作業工数見積もり!G5:G59,"完了",作業工数見積もり!F5:F59)</f>
+        <v>39.25</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -2157,7 +2111,7 @@
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1</v>
+        <v>1.0328947368421053</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -2175,7 +2129,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>45982</v>
+        <v>45984</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -2196,11 +2150,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>1.2285714285714286</v>
+        <v>1.1764705882352942</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -2213,11 +2167,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>1.075</v>
+        <v>1.0256410256410255</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -2230,11 +2184,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>0.84313725490196079</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -2318,7 +2272,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M109"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="B2:M105"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="33"/>
   <cols>
     <col min="1" max="1" width="9.75" style="14"/>
@@ -2335,7 +2290,7 @@
     <col min="12" max="16384" width="9.75" style="14"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
+    <row r="2" spans="2:13" ht="33.75" thickBot="1">
       <c r="B2" s="16" t="s">
         <v>30</v>
       </c>
@@ -2355,12 +2310,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" ht="33.75" hidden="1" thickBot="1">
       <c r="B3" s="50" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>4</v>
@@ -2372,15 +2327,15 @@
         <v>2</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" ht="33.75" thickBot="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="33.75" hidden="1" thickBot="1">
       <c r="B4" s="50" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>4</v>
@@ -2392,7 +2347,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I4" s="20"/>
       <c r="J4" s="20"/>
@@ -2424,7 +2379,7 @@
       </c>
       <c r="J5" s="24">
         <f>SUM(J6,J7,J8)</f>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K5" s="25"/>
       <c r="L5" s="62"/>
@@ -2454,8 +2409,8 @@
         <v>27</v>
       </c>
       <c r="J6" s="28">
-        <f>COUNTIF(E5:E106,I6)</f>
-        <v>49</v>
+        <f>COUNTIF(E5:E102,I6)</f>
+        <v>45</v>
       </c>
       <c r="K6" s="29"/>
       <c r="L6" s="63"/>
@@ -2485,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="28">
-        <f>COUNTIF(E5:E106,I7)</f>
+        <f>COUNTIF(E5:E102,I7)</f>
         <v>24</v>
       </c>
       <c r="K7" s="29"/>
@@ -2516,14 +2471,14 @@
         <v>28</v>
       </c>
       <c r="J8" s="28">
-        <f>COUNTIF(E5:E106,I8)</f>
+        <f>COUNTIF(E5:E102,I8)</f>
         <v>11</v>
       </c>
       <c r="K8" s="29"/>
       <c r="L8" s="63"/>
       <c r="M8" s="26"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" hidden="1">
       <c r="B9" s="21" t="s">
         <v>47</v>
       </c>
@@ -2540,19 +2495,19 @@
         <v>1</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H9" s="22"/>
       <c r="I9" s="32" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="28">
-        <f>COUNTIF(G5:G106,I9)</f>
-        <v>59</v>
+        <f>COUNTIF(G5:G102,I9)</f>
+        <v>61</v>
       </c>
       <c r="K9" s="33">
         <f>J9/J5</f>
-        <v>0.70238095238095233</v>
+        <v>0.76249999999999996</v>
       </c>
       <c r="L9" s="63"/>
       <c r="M9" s="26"/>
@@ -2581,17 +2536,17 @@
         <v>41</v>
       </c>
       <c r="J10" s="28">
-        <f>COUNTIF(G5:G106,I10)</f>
-        <v>25</v>
+        <f>COUNTIF(G5:G102,I10)</f>
+        <v>18</v>
       </c>
       <c r="K10" s="35">
         <f>(J10+J11)/J5</f>
-        <v>0.29761904761904762</v>
+        <v>0.23749999999999999</v>
       </c>
       <c r="L10" s="63"/>
       <c r="M10" s="26"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" hidden="1">
       <c r="B11" s="36" t="s">
         <v>43</v>
       </c>
@@ -2608,21 +2563,21 @@
         <v>0.25</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H11" s="22"/>
       <c r="I11" s="37" t="s">
         <v>42</v>
       </c>
       <c r="J11" s="19">
-        <f>COUNTIF(G5:G106,I11)</f>
-        <v>0</v>
+        <f>COUNTIF(G5:G102,I11)</f>
+        <v>1</v>
       </c>
       <c r="K11" s="29"/>
       <c r="L11" s="63"/>
       <c r="M11" s="26"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" hidden="1">
       <c r="B12" s="36" t="s">
         <v>43</v>
       </c>
@@ -2639,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H12" s="22"/>
       <c r="I12" s="38"/>
@@ -2648,7 +2603,7 @@
       <c r="L12" s="63"/>
       <c r="M12" s="26"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" hidden="1">
       <c r="B13" s="36" t="s">
         <v>43</v>
       </c>
@@ -2665,21 +2620,21 @@
         <v>0.25</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H13" s="22"/>
       <c r="I13" s="39" t="s">
         <v>44</v>
       </c>
       <c r="J13" s="19">
-        <f>SUM(F5:F106)</f>
-        <v>81</v>
+        <f>SUM(F5:F102)</f>
+        <v>79.25</v>
       </c>
       <c r="K13" s="29"/>
       <c r="L13" s="63"/>
       <c r="M13" s="26"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" hidden="1">
       <c r="B14" s="36" t="s">
         <v>43</v>
       </c>
@@ -2696,7 +2651,7 @@
         <v>0.25</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H14" s="22"/>
       <c r="I14" s="57" t="s">
@@ -2704,13 +2659,13 @@
       </c>
       <c r="J14" s="19">
         <f>8*J13</f>
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="K14" s="29"/>
       <c r="L14" s="63"/>
       <c r="M14" s="26"/>
     </row>
-    <row r="15" spans="2:13" ht="35.25">
+    <row r="15" spans="2:13" ht="35.25" hidden="1">
       <c r="B15" s="36" t="s">
         <v>43</v>
       </c>
@@ -2727,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H15" s="22"/>
       <c r="I15" s="58" t="s">
@@ -2738,12 +2693,12 @@
       <c r="L15" s="63"/>
       <c r="M15" s="26"/>
     </row>
-    <row r="16" spans="2:13" ht="36" thickBot="1">
+    <row r="16" spans="2:13" ht="36" hidden="1" thickBot="1">
       <c r="B16" s="36" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>4</v>
@@ -2755,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H16" s="22"/>
       <c r="I16" s="59" t="s">
@@ -2766,12 +2721,12 @@
       <c r="L16" s="64"/>
       <c r="M16" s="26"/>
     </row>
-    <row r="17" spans="2:12" ht="35.25">
+    <row r="17" spans="2:12" ht="35.25" hidden="1">
       <c r="B17" s="36" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>4</v>
@@ -2783,19 +2738,19 @@
         <v>1</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I17" s="56"/>
       <c r="J17" s="42"/>
       <c r="K17" s="42"/>
       <c r="L17" s="42"/>
     </row>
-    <row r="18" spans="2:12" ht="35.25">
+    <row r="18" spans="2:12" ht="35.25" hidden="1">
       <c r="B18" s="44" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>4</v>
@@ -2807,16 +2762,16 @@
         <v>0.25</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I18" s="55"/>
     </row>
-    <row r="19" spans="2:12" ht="35.25">
+    <row r="19" spans="2:12" ht="35.25" hidden="1">
       <c r="B19" s="44" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>4</v>
@@ -2828,16 +2783,16 @@
         <v>0.25</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I19" s="55"/>
     </row>
-    <row r="20" spans="2:12" ht="35.25">
+    <row r="20" spans="2:12" ht="35.25" hidden="1">
       <c r="B20" s="44" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>4</v>
@@ -2849,16 +2804,16 @@
         <v>0.25</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I20" s="55"/>
     </row>
-    <row r="21" spans="2:12" ht="35.25">
+    <row r="21" spans="2:12" ht="35.25" hidden="1">
       <c r="B21" s="44" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>4</v>
@@ -2870,11 +2825,11 @@
         <v>0.25</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I21" s="55"/>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:12" hidden="1">
       <c r="B22" s="43" t="s">
         <v>53</v>
       </c>
@@ -2891,15 +2846,15 @@
         <v>0.25</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" hidden="1">
       <c r="B23" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>4</v>
@@ -2911,15 +2866,15 @@
         <v>0.5</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" hidden="1">
       <c r="B24" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>4</v>
@@ -2931,15 +2886,15 @@
         <v>3</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" hidden="1">
       <c r="B25" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>4</v>
@@ -2951,15 +2906,15 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" hidden="1">
       <c r="B26" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>4</v>
@@ -2971,15 +2926,15 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" hidden="1">
       <c r="B27" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>4</v>
@@ -2991,15 +2946,15 @@
         <v>0.25</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" hidden="1">
       <c r="B28" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>4</v>
@@ -3011,15 +2966,15 @@
         <v>0.25</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" hidden="1">
       <c r="B29" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>4</v>
@@ -3031,7 +2986,7 @@
         <v>0.25</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -3039,10 +2994,10 @@
         <v>53</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>16</v>
@@ -3054,7 +3009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
+    <row r="31" spans="2:12" hidden="1">
       <c r="B31" s="43" t="s">
         <v>53</v>
       </c>
@@ -3071,10 +3026,10 @@
         <v>2</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" hidden="1">
       <c r="B32" s="43" t="s">
         <v>53</v>
       </c>
@@ -3091,15 +3046,15 @@
         <v>1</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" hidden="1">
       <c r="B33" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>4</v>
@@ -3111,10 +3066,10 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" hidden="1">
       <c r="B34" s="43" t="s">
         <v>53</v>
       </c>
@@ -3131,10 +3086,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" hidden="1">
       <c r="B35" s="43" t="s">
         <v>53</v>
       </c>
@@ -3151,15 +3106,15 @@
         <v>1</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" hidden="1">
       <c r="B36" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>4</v>
@@ -3171,15 +3126,15 @@
         <v>1</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" hidden="1">
       <c r="B37" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>4</v>
@@ -3191,10 +3146,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" hidden="1">
       <c r="B38" s="43" t="s">
         <v>53</v>
       </c>
@@ -3211,10 +3166,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" hidden="1">
       <c r="B39" s="43" t="s">
         <v>53</v>
       </c>
@@ -3231,10 +3186,10 @@
         <v>1</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" hidden="1">
       <c r="B40" s="43" t="s">
         <v>62</v>
       </c>
@@ -3251,38 +3206,38 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" hidden="1">
       <c r="B41" s="43" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F41" s="15">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="43" t="s">
-        <v>62</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" hidden="1">
+      <c r="B42" s="45" t="s">
+        <v>98</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>16</v>
@@ -3291,38 +3246,38 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="43" t="s">
-        <v>62</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" hidden="1">
+      <c r="B43" s="45" t="s">
+        <v>98</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>16</v>
       </c>
       <c r="F43" s="15">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="43" t="s">
-        <v>62</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" hidden="1">
+      <c r="B44" s="45" t="s">
+        <v>98</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>16</v>
@@ -3331,35 +3286,35 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="43" t="s">
-        <v>53</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" hidden="1">
+      <c r="B45" s="45" t="s">
+        <v>77</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F45" s="15">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" hidden="1">
       <c r="B46" s="45" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>4</v>
@@ -3368,58 +3323,58 @@
         <v>16</v>
       </c>
       <c r="F46" s="15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" s="45" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F47" s="15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="2:7">
       <c r="B48" s="45" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>85</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F48" s="15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" hidden="1">
       <c r="B49" s="45" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>4</v>
@@ -3431,95 +3386,95 @@
         <v>1</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" hidden="1">
       <c r="B50" s="45" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F50" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" hidden="1">
       <c r="B51" s="45" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F51" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="45" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F52" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="45" t="s">
-        <v>145</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" hidden="1">
+      <c r="B53" s="46" t="s">
+        <v>88</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F53" s="15">
         <v>1</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7">
-      <c r="B54" s="45" t="s">
-        <v>146</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" hidden="1">
+      <c r="B54" s="46" t="s">
+        <v>46</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>4</v>
@@ -3528,18 +3483,18 @@
         <v>9</v>
       </c>
       <c r="F54" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7">
-      <c r="B55" s="45" t="s">
-        <v>147</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" hidden="1">
+      <c r="B55" s="46" t="s">
+        <v>46</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>4</v>
@@ -3548,18 +3503,18 @@
         <v>9</v>
       </c>
       <c r="F55" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="2:7">
-      <c r="B56" s="45" t="s">
-        <v>148</v>
+      <c r="B56" s="46" t="s">
+        <v>46</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>4</v>
@@ -3568,7 +3523,7 @@
         <v>9</v>
       </c>
       <c r="F56" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G56" s="15" t="s">
         <v>35</v>
@@ -3576,7 +3531,7 @@
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="46" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>139</v>
@@ -3588,15 +3543,15 @@
         <v>9</v>
       </c>
       <c r="F57" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="46" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>140</v>
@@ -3608,18 +3563,18 @@
         <v>9</v>
       </c>
       <c r="F58" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7">
-      <c r="B59" s="46" t="s">
-        <v>46</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" hidden="1">
+      <c r="B59" s="47" t="s">
+        <v>89</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D59" s="15" t="s">
         <v>4</v>
@@ -3628,38 +3583,38 @@
         <v>9</v>
       </c>
       <c r="F59" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" hidden="1">
+      <c r="B60" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="15">
         <v>1</v>
       </c>
-      <c r="G59" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7">
-      <c r="B60" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E60" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="15">
-        <v>3</v>
-      </c>
       <c r="G60" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7">
-      <c r="B61" s="46" t="s">
-        <v>92</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" hidden="1">
+      <c r="B61" s="47" t="s">
+        <v>89</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="D61" s="15" t="s">
         <v>4</v>
@@ -3668,58 +3623,58 @@
         <v>9</v>
       </c>
       <c r="F61" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7">
-      <c r="B62" s="46" t="s">
-        <v>92</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" hidden="1">
+      <c r="B62" s="54" t="s">
+        <v>126</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F62" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7">
-      <c r="B63" s="47" t="s">
-        <v>93</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" hidden="1">
+      <c r="B63" s="54" t="s">
+        <v>126</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D63" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F63" s="15">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7">
-      <c r="B64" s="47" t="s">
-        <v>93</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" hidden="1">
+      <c r="B64" s="54" t="s">
+        <v>126</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>4</v>
@@ -3731,221 +3686,221 @@
         <v>1</v>
       </c>
       <c r="G64" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7">
+      <c r="B65" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G65" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7">
+      <c r="B66" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="15" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="65" spans="2:7">
-      <c r="B65" s="47" t="s">
+      <c r="F66" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" hidden="1">
+      <c r="B67" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C67" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="C65" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E65" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="15">
-        <v>1</v>
-      </c>
-      <c r="G65" s="15" t="s">
+      <c r="D67" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" s="15" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="66" spans="2:7">
-      <c r="B66" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F66" s="15">
-        <v>1</v>
-      </c>
-      <c r="G66" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7">
-      <c r="B67" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E67" s="15" t="s">
-        <v>16</v>
       </c>
       <c r="F67" s="15">
         <v>1</v>
       </c>
       <c r="G67" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" hidden="1">
+      <c r="B68" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E68" s="15" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="68" spans="2:7">
-      <c r="B68" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E68" s="15" t="s">
-        <v>16</v>
       </c>
       <c r="F68" s="15">
         <v>1</v>
       </c>
       <c r="G68" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" hidden="1">
+      <c r="B69" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E69" s="15" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="69" spans="2:7">
-      <c r="B69" s="48" t="s">
+      <c r="F69" s="15">
+        <v>1</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" hidden="1">
+      <c r="B70" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C69" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E69" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G69" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7">
-      <c r="B70" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>96</v>
-      </c>
       <c r="D70" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F70" s="15">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" spans="2:7">
       <c r="B71" s="49" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D71" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F71" s="15">
         <v>1</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="2:7">
       <c r="B72" s="49" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D72" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>119</v>
+        <v>9</v>
       </c>
       <c r="F72" s="15">
         <v>1</v>
       </c>
       <c r="G72" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" hidden="1">
+      <c r="B73" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E73" s="15" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7">
-      <c r="B73" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E73" s="15" t="s">
-        <v>119</v>
       </c>
       <c r="F73" s="15">
         <v>1</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74" spans="2:7">
       <c r="B74" s="49" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F74" s="15">
         <v>1</v>
       </c>
       <c r="G74" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7">
+      <c r="B75" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E75" s="15" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7">
-      <c r="B75" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E75" s="15" t="s">
-        <v>119</v>
       </c>
       <c r="F75" s="15">
         <v>1</v>
@@ -3955,17 +3910,17 @@
       </c>
     </row>
     <row r="76" spans="2:7">
-      <c r="B76" s="49" t="s">
+      <c r="B76" s="51" t="s">
         <v>103</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="F76" s="15">
         <v>1</v>
@@ -3975,262 +3930,207 @@
       </c>
     </row>
     <row r="77" spans="2:7">
-      <c r="B77" s="49" t="s">
+      <c r="B77" s="51" t="s">
         <v>103</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D77" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F77" s="15">
         <v>1</v>
       </c>
       <c r="G77" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7">
-      <c r="B78" s="49" t="s">
-        <v>103</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" hidden="1">
+      <c r="B78" s="52" t="s">
+        <v>107</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="F78" s="15">
         <v>1</v>
       </c>
       <c r="G78" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="79" spans="2:7">
-      <c r="B79" s="51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" hidden="1">
+      <c r="B79" s="52" t="s">
         <v>107</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="F79" s="15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="80" spans="2:7">
-      <c r="B80" s="51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" hidden="1">
+      <c r="B80" s="52" t="s">
         <v>107</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="F80" s="15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7">
-      <c r="B81" s="51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" hidden="1">
+      <c r="B81" s="52" t="s">
         <v>107</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D81" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>119</v>
+        <v>9</v>
       </c>
       <c r="F81" s="15">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G81" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7">
-      <c r="B82" s="52" t="s">
-        <v>111</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" hidden="1">
+      <c r="B82" s="53" t="s">
+        <v>117</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D82" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F82" s="15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7">
-      <c r="B83" s="52" t="s">
-        <v>111</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" hidden="1">
+      <c r="B83" s="53" t="s">
+        <v>117</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D83" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F83" s="15">
         <v>0.5</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7">
-      <c r="B84" s="52" t="s">
-        <v>111</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" hidden="1">
+      <c r="B84" s="53" t="s">
+        <v>117</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F84" s="15">
         <v>0.5</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7">
-      <c r="B85" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="C85" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E85" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" s="15">
-        <v>0.25</v>
-      </c>
-      <c r="G85" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7">
-      <c r="B86" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G86" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7">
-      <c r="B87" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E87" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G87" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7">
-      <c r="B88" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E88" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G88" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="100" spans="3:7">
-      <c r="C100" s="18"/>
-    </row>
-    <row r="109" spans="3:7">
-      <c r="G109" s="40"/>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" hidden="1"/>
+    <row r="86" spans="2:7" hidden="1"/>
+    <row r="87" spans="2:7" hidden="1"/>
+    <row r="88" spans="2:7" hidden="1"/>
+    <row r="89" spans="2:7" hidden="1"/>
+    <row r="90" spans="2:7" hidden="1"/>
+    <row r="91" spans="2:7" hidden="1"/>
+    <row r="92" spans="2:7" hidden="1"/>
+    <row r="93" spans="2:7" hidden="1"/>
+    <row r="94" spans="2:7" hidden="1"/>
+    <row r="95" spans="2:7" hidden="1"/>
+    <row r="96" spans="2:7" hidden="1">
+      <c r="C96" s="18"/>
+    </row>
+    <row r="97" spans="7:7" hidden="1"/>
+    <row r="98" spans="7:7" hidden="1"/>
+    <row r="99" spans="7:7" hidden="1"/>
+    <row r="100" spans="7:7" hidden="1"/>
+    <row r="101" spans="7:7" hidden="1"/>
+    <row r="102" spans="7:7" hidden="1"/>
+    <row r="103" spans="7:7" hidden="1"/>
+    <row r="104" spans="7:7" hidden="1"/>
+    <row r="105" spans="7:7">
+      <c r="G105" s="40"/>
     </row>
   </sheetData>
-  <autoFilter ref="C2:G108" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="C2:G104" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="未着手"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D108" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D104" xr:uid="{AF10AFEC-2E3A-4CB7-ABD8-6255C47E78C2}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E108" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E104" xr:uid="{8982FD40-CA4D-4B92-93FE-B37B6B67ACD6}">
       <formula1>"プロト,アルファ,ベータ,マスタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G108" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G104" xr:uid="{E1CFE88F-4F87-4696-BE21-1133C2AEB8C1}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
   </dataValidations>

--- a/コスト表.xlsx
+++ b/コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lovecap\Documents\GitHub\NierGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7813B467-8A8E-4091-A402-3631BAB20A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E1010D-E42A-4FDC-A20D-B7ADDF25E4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>1.0328947368421053</v>
+        <v>1.0064102564102564</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>45984</v>
+        <v>45985</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -2503,11 +2503,11 @@
       </c>
       <c r="J9" s="28">
         <f>COUNTIF(G5:G102,I9)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" s="33">
         <f>J9/J5</f>
-        <v>0.76249999999999996</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="L9" s="63"/>
       <c r="M9" s="26"/>
@@ -2537,11 +2537,11 @@
       </c>
       <c r="J10" s="28">
         <f>COUNTIF(G5:G102,I10)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K10" s="35">
         <f>(J10+J11)/J5</f>
-        <v>0.23749999999999999</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="L10" s="63"/>
       <c r="M10" s="26"/>
@@ -3329,7 +3329,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" hidden="1">
       <c r="B47" s="45" t="s">
         <v>80</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" hidden="1">
       <c r="B52" s="45" t="s">
         <v>144</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="71" spans="2:7">
+    <row r="71" spans="2:7" hidden="1">
       <c r="B71" s="49" t="s">
         <v>99</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" spans="2:7">
@@ -4149,6 +4149,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="04574505-c322-4981-8ebb-5d25af8d4de8" xsi:nil="true"/>
+    <_x8a73__x7d30_ xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101009C7952A5A25B2543AB99BC9B879A46ED" ma:contentTypeVersion="16" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="18ce886227b4f7d0c1a56646945dc47e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xmlns:ns3="04574505-c322-4981-8ebb-5d25af8d4de8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5be0a050d98fc17aa9c3986a154fc28" ns2:_="" ns3:_="">
     <xsd:import namespace="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
@@ -4391,18 +4403,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="04574505-c322-4981-8ebb-5d25af8d4de8" xsi:nil="true"/>
-    <_x8a73__x7d30_ xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
   <ds:schemaRefs>
@@ -4412,6 +4412,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="04574505-c322-4981-8ebb-5d25af8d4de8"/>
+    <ds:schemaRef ds:uri="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F472F951-64CD-40D8-896F-068DA14071AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4428,15 +4439,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="04574505-c322-4981-8ebb-5d25af8d4de8"/>
-    <ds:schemaRef ds:uri="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>